--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -7,20 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Setup" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Trend" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ref" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signature" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Start Here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Setup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Scenarios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Trend" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ref" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signature" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1. Setup'!$A$1:$H$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2. Dashboard'!$A$1:$H$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3. Scenarios'!$A$1:$F$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'4. Trend'!$A$1:$M$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Ref'!$A$1:$D$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Signature'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'0. Start Here'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1. Setup'!$A$1:$H$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Dashboard'!$A$1:$H$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'3. Scenarios'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'4. Trend'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Ref'!$A$1:$D$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Signature'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +36,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +137,32 @@
       <color rgb="001A1A1A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="004A5A6A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B3261E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -173,8 +199,13 @@
         <fgColor rgb="00EAEEF2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9A227"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -196,11 +227,88 @@
         <color rgb="00C7D0D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C7D0D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C7D0D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C7D0D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C7D0D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C7D0D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C7D0D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C7D0D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C7D0D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C7D0D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C7D0D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C7D0D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C7D0D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C7D0D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C7D0D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -211,6 +319,45 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -235,6 +382,9 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -253,9 +403,6 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -326,9 +473,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1025,6 +1169,578 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>START HERE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>You do not need to understand accounting to use this. Fill eight numbers and read the verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THIS IS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>A CFO in a spreadsheet. You type what your business earned and spent. It tells you whether you are making money, whether each order makes money, how long your cash lasts, and what to fix first.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>THREE STEPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Go to the sheet '1. Setup'. Type over the YELLOW cells only.</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Everything that is not yellow calculates itself. You cannot break it by typing in yellow.</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Start with the eight numbers marked START HERE in column C.</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>The other rows are already filled with example numbers. Replace them as you find them; the dashboard works before you finish.</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Read '2. Dashboard' from the top.</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>The coloured banner names your single biggest problem in one sentence.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="8" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>THE EIGHT NUMBERS YOU REALLY NEED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>On '1. Setup'</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>What it means in plain words</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Where to find it</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Gross Revenue</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Everything customers paid you, before refunds.</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Your sales report or bank deposits</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Product / Material (LANDED)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>What the goods cost you delivered to your door - price plus freight plus duty, not the invoice alone.</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Supplier invoices plus shipping and customs</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Outbound Shipping</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Courier cost you actually pay, after what the customer covers.</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Courier bill</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Advertising Spend</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Every platform added together.</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Meta, Google, TikTok billing</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Salaries (non-production)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>People who are paid whether or not you sell anything.</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Shop, office or warehouse.</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Rent receipt</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Number of Orders</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>How many orders in the period. This turns totals into per-order economics.</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Order dashboard</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Cash &amp; Bank (closing)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>What is actually in the bank on the last day.</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Bank statement</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>WHAT EACH SHEET DOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>1. Setup</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Where you type. Yellow cells only.</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>2. Dashboard</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>The answer. Profit, unit economics, cash, runway, verdict.</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>3. Scenarios</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>What if sales fall 25%? What if ads get cheaper?</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>4. Trend</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Twelve months side by side. Is it getting better or worse?</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>The 34-currency table. You do not need to touch it.</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Who built this. Locked.</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>READ THIS BEFORE YOU TRUST THE NUMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Profit is not cash. You can show a profit here and still have an empty bank account, because loan principal, owner drawings and stock purchases spend cash without appearing as costs. If the profit line and your bank balance disagree, believe the bank.</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="8" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>বাংলা:  শুধু হলুদ ঘরগুলোতে আপনার সংখ্যা লিখুন। বাকি সব নিজে হিসাব হয়ে যাবে। '২. Dashboard' শীটে গিয়ে উপরের রঙিন লাইনটা পড়ুন — ওখানে আপনার সবচেয়ে বড় সমস্যাটা এক লাইনে লেখা থাকবে।</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="8" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0" footer="0"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7B45"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1063,46 +1779,46 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Select currency</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>BDT</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Symbol (auto)</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="21">
         <f>IFERROR(INDEX(Ref!$B$2:$B$35,MATCH($B$5,Ref!$A$2:$A$35,0)),"?")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Currency name (auto)</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="22">
         <f>IFERROR(INDEX(Ref!$C$2:$C$35,MATCH($B$5,Ref!$A$2:$A$35,0)),"Unknown")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Reporting period</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>2026-03 (monthly)</t>
         </is>
@@ -1116,74 +1832,74 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Gross Revenue</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="26" t="n">
         <v>920000</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>All sales before returns</t>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Returns &amp; Refunds</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="26" t="n">
         <v>70000</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Enter positive</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Discounts Given</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
+      <c r="C14" s="28" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="30">
         <f>B12-B13-B14</f>
         <v/>
       </c>
-      <c r="C15" s="13" t="n"/>
+      <c r="C15" s="29" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1193,74 +1909,74 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Product / Material (LANDED)</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="26" t="n">
         <v>380000</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>incl. freight, duty, clearing</t>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Direct Labour</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="26" t="n">
         <v>40000</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>Production staff only</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="26" t="n">
         <v>22000</v>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
+      <c r="C21" s="28" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>TOTAL COGS</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="30">
         <f>SUM(B19:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="13" t="n"/>
+      <c r="C22" s="29" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1270,89 +1986,89 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Outbound Shipping</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="26" t="n">
         <v>102000</v>
       </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Your share</t>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Payment Gateway Fees</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="26" t="n">
         <v>21250</v>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>% + fixed</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Marketplace Commission</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="12" t="inlineStr"/>
+      <c r="C28" s="28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>RTO / Failed Delivery</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Two-way shipping loss</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>TOTAL OTHER VARIABLE</t>
         </is>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="30">
         <f>SUM(B26:B29)</f>
         <v/>
       </c>
-      <c r="C30" s="13" t="n"/>
+      <c r="C30" s="29" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -1362,122 +2078,130 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Advertising Spend</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B34" s="26" t="n">
         <v>240000</v>
       </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>All platforms</t>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Salaries (non-production)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="n">
+      <c r="B35" s="26" t="n">
         <v>95000</v>
       </c>
-      <c r="C35" s="12" t="inlineStr"/>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Owner Compensation</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n">
+      <c r="B36" s="26" t="n">
         <v>40000</v>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>Market rate even if unpaid</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B37" s="26" t="n">
         <v>25000</v>
       </c>
-      <c r="C37" s="12" t="inlineStr"/>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Software &amp; Subscriptions</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B38" s="26" t="n">
         <v>8000</v>
       </c>
-      <c r="C38" s="12" t="inlineStr"/>
+      <c r="C38" s="28" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Other Operating</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B39" s="26" t="n">
         <v>12000</v>
       </c>
-      <c r="C39" s="12" t="inlineStr"/>
+      <c r="C39" s="28" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B40" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>Non-cash</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>TOTAL OPEX</t>
         </is>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="30">
         <f>SUM(B34:B40)</f>
         <v/>
       </c>
-      <c r="C41" s="13" t="n"/>
+      <c r="C41" s="29" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -1487,88 +2211,88 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B45" s="26" t="n">
         <v>12000</v>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>P&amp;L item</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n">
+      <c r="B46" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C46" s="12" t="inlineStr"/>
+      <c r="C46" s="28" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>Loan Principal Repaid</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="26" t="n">
         <v>35000</v>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>CASH ONLY — not a P&amp;L expense</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B48" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>Cash only</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>Owner Drawings</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B49" s="26" t="n">
         <v>60000</v>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>CASH ONLY — not a P&amp;L expense</t>
         </is>
@@ -1582,208 +2306,212 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="24" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>Number of Orders</t>
         </is>
       </c>
-      <c r="B53" s="15" t="n">
+      <c r="B53" s="31" t="n">
         <v>1700</v>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>New Customers</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>New Customers</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Repeat Customers</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Repeat Customers</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Customers Lost (churn)</t>
+        </is>
+      </c>
+      <c r="B56" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Customers Lost (churn)</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="C56" s="12" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Customers at Period Start</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Customers at Period Start</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-    </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>Cash &amp; Bank (closing)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n">
+      <c r="B58" s="26" t="n">
         <v>850000</v>
       </c>
-      <c r="C58" s="12" t="inlineStr"/>
+      <c r="C58" s="27" t="inlineStr">
+        <is>
+          <t>◀ START HERE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>Accounts Receivable (avg)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n">
+      <c r="B59" s="26" t="n">
         <v>310000</v>
       </c>
-      <c r="C59" s="12" t="inlineStr"/>
+      <c r="C59" s="28" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>Inventory at Cost (avg)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B60" s="26" t="n">
         <v>640000</v>
       </c>
-      <c r="C60" s="12" t="inlineStr"/>
+      <c r="C60" s="28" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>Accounts Payable (avg)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="n">
+      <c r="B61" s="26" t="n">
         <v>220000</v>
       </c>
-      <c r="C61" s="12" t="inlineStr"/>
+      <c r="C61" s="28" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="B62" s="11" t="n">
+      <c r="B62" s="26" t="n">
         <v>700000</v>
       </c>
-      <c r="C62" s="12" t="inlineStr"/>
+      <c r="C62" s="28" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B63" s="11" t="n">
+      <c r="B63" s="26" t="n">
         <v>1800000</v>
       </c>
-      <c r="C63" s="12" t="inlineStr"/>
+      <c r="C63" s="28" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B64" s="11" t="n">
+      <c r="B64" s="26" t="n">
         <v>950000</v>
       </c>
-      <c r="C64" s="12" t="inlineStr"/>
+      <c r="C64" s="28" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B65" s="11" t="n">
+      <c r="B65" s="26" t="n">
         <v>1400000</v>
       </c>
-      <c r="C65" s="12" t="inlineStr"/>
+      <c r="C65" s="28" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>Days in Period</t>
         </is>
       </c>
-      <c r="B66" s="16" t="n">
+      <c r="B66" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="28" t="inlineStr">
         <is>
           <t>30 / 90 / 365</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>LEGEND — Yellow fill + blue text = your input. Grey = calculated, do not edit. All figures in the currency chosen at B5.</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n"/>
-      <c r="C68" s="17" t="n"/>
+      <c r="B68" s="33" t="n"/>
+      <c r="C68" s="33" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
@@ -1817,9 +2545,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F2438"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1851,17 +2580,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19">
+      <c r="A3" s="34">
         <f>""&amp;'1. Setup'!$B$6&amp;"  ·  Period: "&amp;'1. Setup'!$B$8</f>
         <v/>
       </c>
-      <c r="B3" s="20" t="n"/>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="n"/>
+      <c r="B3" s="35" t="n"/>
+      <c r="C3" s="35" t="n"/>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1876,231 +2605,231 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="36">
         <f>'1. Setup'!$B$15</f>
         <v/>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="37">
         <f>IF(B7&gt;0,"OK",IF(B7=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="38">
         <f>IFERROR('1. Setup'!$B$15/'1. Setup'!$B$53,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="36">
         <f>'1. Setup'!$B$15-'1. Setup'!$B$22</f>
         <v/>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="37">
         <f>IF(B8&gt;0,"OK",IF(B8=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Blended CAC</t>
         </is>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="38">
         <f>IFERROR('1. Setup'!$B$34/'1. Setup'!$B$54,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Contribution (pre-ad)</t>
         </is>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="36">
         <f>'1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="37">
         <f>IF(B9&gt;0,"OK",IF(B9=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>CM per order</t>
         </is>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="38">
         <f>IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$34)/'1. Setup'!$B$53,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>CM after Ads</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="36">
         <f>'1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$34</f>
         <v/>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="37">
         <f>IF(B10&gt;0,"OK",IF(B10=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>CM ratio (pre-ad)</t>
         </is>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="39">
         <f>IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30)/'1. Setup'!$B$15,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Operating Profit</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="36">
         <f>'1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41</f>
         <v/>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="37">
         <f>IF(B11&gt;0,"OK",IF(B11=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Break-even ROAS</t>
         </is>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="40">
         <f>IFERROR('1. Setup'!$B$15/('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Net Profit</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="36">
         <f>'1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46</f>
         <v/>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="37">
         <f>IF(B12&gt;0,"OK",IF(B12=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Actual ROAS (blended)</t>
         </is>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="40">
         <f>IFERROR('1. Setup'!$B$15/'1. Setup'!$B$34,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Gross Margin</t>
         </is>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="41">
         <f>IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22)/'1. Setup'!$B$15,0)</f>
         <v/>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="37">
         <f>IF(B13&gt;0,"OK",IF(B13=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>ROAS headroom</t>
         </is>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="40">
         <f>IFERROR('1. Setup'!$B$15/'1. Setup'!$B$34-'1. Setup'!$B$15/('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Net Margin</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="41">
         <f>IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46)/'1. Setup'!$B$15,0)</f>
         <v/>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="37">
         <f>IF(B14&gt;0,"OK",IF(B14=0,"FLAT","LOSS"))</f>
         <v/>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Repeat rate</t>
         </is>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="39">
         <f>IFERROR('1. Setup'!$B$55/('1. Setup'!$B$54+'1. Setup'!$B$55),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Churn rate</t>
         </is>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="39">
         <f>IFERROR('1. Setup'!$B$56/'1. Setup'!$B$57,0)</f>
         <v/>
       </c>
@@ -2118,181 +2847,181 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Operating Cash Flow (approx)</t>
         </is>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="42">
         <f>('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46)+'1. Setup'!$B$40</f>
         <v/>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="37">
         <f>IF(ISTEXT(B18),"OK",IF(B18&gt;=0,"OK","LOSS"))</f>
         <v/>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Current Ratio</t>
         </is>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="43">
         <f>IFERROR('1. Setup'!$B$63/'1. Setup'!$B$64,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Cash out below the line</t>
         </is>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="42">
         <f>'1. Setup'!$B$47+'1. Setup'!$B$48+'1. Setup'!$B$49</f>
         <v/>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="37">
         <f>IF(ISTEXT(B19),"OK",IF(B19&gt;=0,"OK","LOSS"))</f>
         <v/>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Quick Ratio</t>
         </is>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="43">
         <f>IFERROR(('1. Setup'!$B$63-'1. Setup'!$B$60)/'1. Setup'!$B$64,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Net Cash Change</t>
         </is>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="42">
         <f>('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46)+'1. Setup'!$B$40-'1. Setup'!$B$47-'1. Setup'!$B$48-'1. Setup'!$B$49</f>
         <v/>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="37">
         <f>IF(ISTEXT(B20),"OK",IF(B20&gt;=0,"OK","LOSS"))</f>
         <v/>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Debt / Equity</t>
         </is>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="43">
         <f>IFERROR('1. Setup'!$B$62/'1. Setup'!$B$65,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Monthly Net Burn</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="42">
         <f>MAX(0,-(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46)+'1. Setup'!$B$40-'1. Setup'!$B$47-'1. Setup'!$B$48-'1. Setup'!$B$49))</f>
         <v/>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="37">
         <f>IF(ISTEXT(B21),"OK",IF(B21&gt;=0,"OK","LOSS"))</f>
         <v/>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>Interest Coverage</t>
         </is>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="40">
         <f>IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41)/'1. Setup'!$B$45,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Runway (months)</t>
         </is>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="44">
         <f>IF(MAX(0,-(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46)+'1. Setup'!$B$40-'1. Setup'!$B$47-'1. Setup'!$B$48-'1. Setup'!$B$49))=0,"cash positive",'1. Setup'!$B$58/MAX(1,-(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30-'1. Setup'!$B$41-'1. Setup'!$B$45-'1. Setup'!$B$46)+'1. Setup'!$B$40-'1. Setup'!$B$47-'1. Setup'!$B$48-'1. Setup'!$B$49)))</f>
         <v/>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="37">
         <f>IF(ISTEXT(B22),"OK",IF(B22&gt;=0,"OK","LOSS"))</f>
         <v/>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>DIO (days)</t>
         </is>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="44">
         <f>IFERROR('1. Setup'!$B$60/'1. Setup'!$B$22*'1. Setup'!$B$66,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>DSO (days)</t>
         </is>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="44">
         <f>IFERROR('1. Setup'!$B$59/'1. Setup'!$B$15*'1. Setup'!$B$66,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>DPO (days)</t>
         </is>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="44">
         <f>IFERROR('1. Setup'!$B$61/'1. Setup'!$B$22*'1. Setup'!$B$66,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>Cash Conversion Cycle</t>
         </is>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="44">
         <f>IFERROR('1. Setup'!$B$60/'1. Setup'!$B$22*'1. Setup'!$B$66+'1. Setup'!$B$59/'1. Setup'!$B$15*'1. Setup'!$B$66-'1. Setup'!$B$61/'1. Setup'!$B$22*'1. Setup'!$B$66,0)</f>
         <v/>
       </c>
@@ -2305,56 +3034,56 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Fixed costs (OPEX excl. ads)</t>
         </is>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="42">
         <f>'1. Setup'!$B$41-'1. Setup'!$B$34</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>CM ratio (pre-ad)</t>
         </is>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="39">
         <f>IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30)/'1. Setup'!$B$15,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Break-even revenue</t>
         </is>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="42">
         <f>IFERROR(B28/B29,0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Break-even orders</t>
         </is>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="45">
         <f>IFERROR(B30/IFERROR('1. Setup'!$B$15/'1. Setup'!$B$53,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="39">
         <f>IFERROR(('1. Setup'!$B$15-B30)/'1. Setup'!$B$15,0)</f>
         <v/>
       </c>
@@ -2367,17 +3096,17 @@
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="31">
+      <c r="A35" s="46">
         <f>IF(B10&lt;0,"BROKEN UNIT ECONOMICS — contribution after ads is negative and actual ROAS is below break-even ROAS. Every order loses money before fixed costs are even counted. Stop scaling; fix pricing, CAC, or COGS first.",IF(B12&lt;0,"NET LOSS FROM OVERHEAD — each order is profitable after ads, but fixed costs, interest, or tax exceed that contribution. Fix overhead, not the product.","PROFITABLE — protect margin and scale toward the next constraint."))</f>
         <v/>
       </c>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
+      <c r="B35" s="46" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
+      <c r="E35" s="46" t="n"/>
+      <c r="F35" s="46" t="n"/>
+      <c r="G35" s="46" t="n"/>
+      <c r="H35" s="46" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
@@ -2421,9 +3150,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001B3A57"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2460,88 +3190,88 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Revenue change</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="47" t="n">
         <v>-0.25</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="47" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>COGS % change</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="47" t="n">
         <v>0.04</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="47" t="n">
         <v>-0.02</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ad spend change</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="47" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Fixed cost change</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="47" t="n">
         <v>0.05</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2553,213 +3283,213 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Net Revenue</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="48">
         <f>'1. Setup'!$B$15*(1+B6)</f>
         <v/>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="48">
         <f>'1. Setup'!$B$15*(1+C6)</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="48">
         <f>'1. Setup'!$B$15*(1+D6)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="48">
         <f>'1. Setup'!$B$22*(1+B6)*(1+B7)</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="48">
         <f>'1. Setup'!$B$22*(1+C6)*(1+C7)</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="48">
         <f>'1. Setup'!$B$22*(1+D6)*(1+D7)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Other variable</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="48">
         <f>'1. Setup'!$B$30*(1+B6)</f>
         <v/>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="48">
         <f>'1. Setup'!$B$30*(1+C6)</f>
         <v/>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="48">
         <f>'1. Setup'!$B$30*(1+D6)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Ad spend</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="48">
         <f>'1. Setup'!$B$34*(1+B8)</f>
         <v/>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="48">
         <f>'1. Setup'!$B$34*(1+C8)</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="48">
         <f>'1. Setup'!$B$34*(1+D8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Fixed OPEX</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="48">
         <f>('1. Setup'!$B$41-'1. Setup'!$B$34)*(1+B9)</f>
         <v/>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="48">
         <f>('1. Setup'!$B$41-'1. Setup'!$B$34)*(1+C9)</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="48">
         <f>('1. Setup'!$B$41-'1. Setup'!$B$34)*(1+D9)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="42">
         <f>B13-B14</f>
         <v/>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="42">
         <f>C13-C14</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="42">
         <f>D13-D14</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Contribution after ads</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="48">
         <f>B13-B14-B15-B16</f>
         <v/>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="48">
         <f>C13-C14-C15-C16</f>
         <v/>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="48">
         <f>D13-D14-D15-D16</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Operating Profit</t>
         </is>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="42">
         <f>B19-B17</f>
         <v/>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="42">
         <f>C19-C17</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="42">
         <f>D19-D17</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Operating Margin</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="49">
         <f>IFERROR(B20/B13,0)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="49">
         <f>IFERROR(C20/C13,0)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="49">
         <f>IFERROR(D20/D13,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="50">
         <f>IF(B20&gt;0,"PROFIT","LOSS")</f>
         <v/>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="50">
         <f>IF(C20&gt;0,"PROFIT","LOSS")</f>
         <v/>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="50">
         <f>IF(D20&gt;0,"PROFIT","LOSS")</f>
         <v/>
       </c>
@@ -2772,57 +3502,57 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Price increase</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Max volume loss tolerable</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="n">
+      <c r="A26" s="51" t="n">
         <v>0.05</v>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="52">
         <f>IFERROR(0.05/(IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30)/'1. Setup'!$B$15,0.3)+0.05),0)</f>
         <v/>
       </c>
-      <c r="C26" s="37" t="n"/>
+      <c r="C26" s="52" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="n">
+      <c r="A27" s="51" t="n">
         <v>0.1</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="52">
         <f>IFERROR(0.1/(IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30)/'1. Setup'!$B$15,0.3)+0.1),0)</f>
         <v/>
       </c>
-      <c r="C27" s="37" t="n"/>
+      <c r="C27" s="52" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="n">
+      <c r="A28" s="51" t="n">
         <v>0.15</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="52">
         <f>IFERROR(0.15/(IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30)/'1. Setup'!$B$15,0.3)+0.15),0)</f>
         <v/>
       </c>
-      <c r="C28" s="37" t="n"/>
+      <c r="C28" s="52" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="n">
+      <c r="A29" s="51" t="n">
         <v>0.2</v>
       </c>
-      <c r="B29" s="37">
+      <c r="B29" s="52">
         <f>IFERROR(0.2/(IFERROR(('1. Setup'!$B$15-'1. Setup'!$B$22-'1. Setup'!$B$30)/'1. Setup'!$B$15,0.3)+0.2),0)</f>
         <v/>
       </c>
-      <c r="C29" s="37" t="n"/>
+      <c r="C29" s="52" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
@@ -2858,9 +3588,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001B3A57"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2897,166 +3628,166 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>Net Revenue</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
+      <c r="H5" s="26" t="n"/>
+      <c r="I5" s="26" t="n"/>
+      <c r="J5" s="26" t="n"/>
+      <c r="K5" s="26" t="n"/>
+      <c r="L5" s="26" t="n"/>
+      <c r="M5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="26" t="n"/>
+      <c r="K6" s="26" t="n"/>
+      <c r="L6" s="26" t="n"/>
+      <c r="M6" s="26" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Variable Costs (shipping, gateway, RTO)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="26" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="26" t="n"/>
+      <c r="I7" s="26" t="n"/>
+      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="26" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Ad Spend</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="26" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>Fixed Operating Costs</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="26" t="n"/>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="26" t="n"/>
+      <c r="K9" s="26" t="n"/>
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="26" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -3066,328 +3797,328 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="55">
         <f>B5-B6-B7</f>
         <v/>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="55">
         <f>C5-C6-C7</f>
         <v/>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="55">
         <f>D5-D6-D7</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="55">
         <f>E5-E6-E7</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="55">
         <f>F5-F6-F7</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="55">
         <f>G5-G6-G7</f>
         <v/>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="55">
         <f>H5-H6-H7</f>
         <v/>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="55">
         <f>I5-I6-I7</f>
         <v/>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="55">
         <f>J5-J6-J7</f>
         <v/>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="55">
         <f>K5-K6-K7</f>
         <v/>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="55">
         <f>L5-L6-L7</f>
         <v/>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="55">
         <f>M5-M6-M7</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>Contribution Margin %</t>
         </is>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="56">
         <f>IFERROR(B11/B5,"")</f>
         <v/>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="56">
         <f>IFERROR(C11/C5,"")</f>
         <v/>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="56">
         <f>IFERROR(D11/D5,"")</f>
         <v/>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="56">
         <f>IFERROR(E11/E5,"")</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="56">
         <f>IFERROR(F11/F5,"")</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="56">
         <f>IFERROR(G11/G5,"")</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="56">
         <f>IFERROR(H11/H5,"")</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="56">
         <f>IFERROR(I11/I5,"")</f>
         <v/>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="56">
         <f>IFERROR(J11/J5,"")</f>
         <v/>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="56">
         <f>IFERROR(K11/K5,"")</f>
         <v/>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="56">
         <f>IFERROR(L11/L5,"")</f>
         <v/>
       </c>
-      <c r="M12" s="41">
+      <c r="M12" s="56">
         <f>IFERROR(M11/M5,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Operating Profit</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="55">
         <f>B11-B8-B9</f>
         <v/>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="55">
         <f>C11-C8-C9</f>
         <v/>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="55">
         <f>D11-D8-D9</f>
         <v/>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="55">
         <f>E11-E8-E9</f>
         <v/>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="55">
         <f>F11-F8-F9</f>
         <v/>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="55">
         <f>G11-G8-G9</f>
         <v/>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="55">
         <f>H11-H8-H9</f>
         <v/>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="55">
         <f>I11-I8-I9</f>
         <v/>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="55">
         <f>J11-J8-J9</f>
         <v/>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="55">
         <f>K11-K8-K9</f>
         <v/>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="55">
         <f>L11-L8-L9</f>
         <v/>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="55">
         <f>M11-M8-M9</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>Operating Margin %</t>
         </is>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="56">
         <f>IFERROR(B13/B5,"")</f>
         <v/>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="56">
         <f>IFERROR(C13/C5,"")</f>
         <v/>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="56">
         <f>IFERROR(D13/D5,"")</f>
         <v/>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="56">
         <f>IFERROR(E13/E5,"")</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="56">
         <f>IFERROR(F13/F5,"")</f>
         <v/>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="56">
         <f>IFERROR(G13/G5,"")</f>
         <v/>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="56">
         <f>IFERROR(H13/H5,"")</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="56">
         <f>IFERROR(I13/I5,"")</f>
         <v/>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="56">
         <f>IFERROR(J13/J5,"")</f>
         <v/>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="56">
         <f>IFERROR(K13/K5,"")</f>
         <v/>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="56">
         <f>IFERROR(L13/L5,"")</f>
         <v/>
       </c>
-      <c r="M14" s="41">
+      <c r="M14" s="56">
         <f>IFERROR(M13/M5,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="54" t="inlineStr">
         <is>
           <t>Cumulative Operating Profit</t>
         </is>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="55">
         <f>B13</f>
         <v/>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="55">
         <f>B15+C13</f>
         <v/>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="55">
         <f>C15+D13</f>
         <v/>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="55">
         <f>D15+E13</f>
         <v/>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="55">
         <f>E15+F13</f>
         <v/>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="55">
         <f>F15+G13</f>
         <v/>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="55">
         <f>G15+H13</f>
         <v/>
       </c>
-      <c r="I15" s="40">
+      <c r="I15" s="55">
         <f>H15+I13</f>
         <v/>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="55">
         <f>I15+J13</f>
         <v/>
       </c>
-      <c r="K15" s="40">
+      <c r="K15" s="55">
         <f>J15+K13</f>
         <v/>
       </c>
-      <c r="L15" s="40">
+      <c r="L15" s="55">
         <f>K15+L13</f>
         <v/>
       </c>
-      <c r="M15" s="40">
+      <c r="M15" s="55">
         <f>L15+M13</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="54" t="inlineStr">
         <is>
           <t>Revenue Growth vs Prior Month %</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr"/>
-      <c r="C16" s="41">
+      <c r="B16" s="56" t="inlineStr"/>
+      <c r="C16" s="56">
         <f>IFERROR(C5/B5-1,"")</f>
         <v/>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="56">
         <f>IFERROR(D5/C5-1,"")</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="56">
         <f>IFERROR(E5/D5-1,"")</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="56">
         <f>IFERROR(F5/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="56">
         <f>IFERROR(G5/F5-1,"")</f>
         <v/>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="56">
         <f>IFERROR(H5/G5-1,"")</f>
         <v/>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="56">
         <f>IFERROR(I5/H5-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="56">
         <f>IFERROR(J5/I5-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="56">
         <f>IFERROR(K5/J5-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="41">
+      <c r="L16" s="56">
         <f>IFERROR(L5/K5-1,"")</f>
         <v/>
       </c>
-      <c r="M16" s="41">
+      <c r="M16" s="56">
         <f>IFERROR(M5/L5-1,"")</f>
         <v/>
       </c>
@@ -3400,23 +4131,23 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="inlineStr">
+      <c r="A37" s="57" t="inlineStr">
         <is>
           <t>Read the direction, not the level. Three months of falling contribution margin is a structural problem; one month is noise.</t>
         </is>
       </c>
-      <c r="B37" s="42" t="n"/>
-      <c r="C37" s="42" t="n"/>
-      <c r="D37" s="42" t="n"/>
-      <c r="E37" s="42" t="n"/>
-      <c r="F37" s="42" t="n"/>
-      <c r="G37" s="42" t="n"/>
-      <c r="H37" s="42" t="n"/>
-      <c r="I37" s="42" t="n"/>
-      <c r="J37" s="42" t="n"/>
-      <c r="K37" s="42" t="n"/>
-      <c r="L37" s="42" t="n"/>
-      <c r="M37" s="42" t="n"/>
+      <c r="B37" s="57" t="n"/>
+      <c r="C37" s="57" t="n"/>
+      <c r="D37" s="57" t="n"/>
+      <c r="E37" s="57" t="n"/>
+      <c r="F37" s="57" t="n"/>
+      <c r="G37" s="57" t="n"/>
+      <c r="H37" s="57" t="n"/>
+      <c r="I37" s="57" t="n"/>
+      <c r="J37" s="57" t="n"/>
+      <c r="K37" s="57" t="n"/>
+      <c r="L37" s="57" t="n"/>
+      <c r="M37" s="57" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
@@ -3444,9 +4175,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C7D0D9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3460,704 +4192,704 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>Decimals</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>BDT</t>
         </is>
       </c>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>৳</t>
         </is>
       </c>
-      <c r="C2" s="43" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Bangladeshi Taka</t>
         </is>
       </c>
-      <c r="D2" s="43" t="n">
+      <c r="D2" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>₹</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Indian Rupee</t>
         </is>
       </c>
-      <c r="D3" s="43" t="n">
+      <c r="D3" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>PKR</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>₨</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Pakistani Rupee</t>
         </is>
       </c>
-      <c r="D4" s="43" t="n">
+      <c r="D4" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>LKR</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Rs</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Sri Lankan Rupee</t>
         </is>
       </c>
-      <c r="D5" s="43" t="n">
+      <c r="D5" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>NPR</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>रू</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Nepalese Rupee</t>
         </is>
       </c>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>US Dollar</t>
         </is>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Euro</t>
         </is>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>£</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Pound Sterling</t>
         </is>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>C$</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Canadian Dollar</t>
         </is>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>AUD</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>A$</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Australian Dollar</t>
         </is>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>AED</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>د.إ</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>UAE Dirham</t>
         </is>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>SR</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Saudi Riyal</t>
         </is>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>QAR</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Qatari Riyal</t>
         </is>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>KWD</t>
         </is>
       </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Kuwaiti Dinar</t>
         </is>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>BHD</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>BD</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Bahraini Dinar</t>
         </is>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>OMR</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Omani Rial</t>
         </is>
       </c>
-      <c r="D17" s="43" t="n">
+      <c r="D17" s="15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>MYR</t>
         </is>
       </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>RM</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Malaysian Ringgit</t>
         </is>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>SGD</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>S$</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Singapore Dollar</t>
         </is>
       </c>
-      <c r="D19" s="43" t="n">
+      <c r="D19" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>THB</t>
         </is>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>฿</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Thai Baht</t>
         </is>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>IDR</t>
         </is>
       </c>
-      <c r="B21" s="43" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Rp</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Indonesian Rupiah</t>
         </is>
       </c>
-      <c r="D21" s="43" t="n">
+      <c r="D21" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>₫</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Vietnamese Dong</t>
         </is>
       </c>
-      <c r="D22" s="43" t="n">
+      <c r="D22" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>PHP</t>
         </is>
       </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>₱</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Philippine Peso</t>
         </is>
       </c>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>CN¥</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Chinese Yuan</t>
         </is>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D24" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>JP¥</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Japanese Yen</t>
         </is>
       </c>
-      <c r="D25" s="43" t="n">
+      <c r="D25" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="B26" s="43" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>₩</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Korean Won</t>
         </is>
       </c>
-      <c r="D26" s="43" t="n">
+      <c r="D26" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>₺</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>Turkish Lira</t>
         </is>
       </c>
-      <c r="D27" s="43" t="n">
+      <c r="D27" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>E£</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>Egyptian Pound</t>
         </is>
       </c>
-      <c r="D28" s="43" t="n">
+      <c r="D28" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>NGN</t>
         </is>
       </c>
-      <c r="B29" s="43" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>₦</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>Nigerian Naira</t>
         </is>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>ZAR</t>
         </is>
       </c>
-      <c r="B30" s="43" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>South African Rand</t>
         </is>
       </c>
-      <c r="D30" s="43" t="n">
+      <c r="D30" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>KES</t>
         </is>
       </c>
-      <c r="B31" s="43" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>KSh</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>Kenyan Shilling</t>
         </is>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="B32" s="43" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Brazilian Real</t>
         </is>
       </c>
-      <c r="D32" s="43" t="n">
+      <c r="D32" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Mex$</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Mexican Peso</t>
         </is>
       </c>
-      <c r="D33" s="43" t="n">
+      <c r="D33" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="B34" s="43" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Swiss Franc</t>
         </is>
       </c>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>SEK</t>
         </is>
       </c>
-      <c r="B35" s="43" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>kr</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Swedish Krona</t>
         </is>
       </c>
-      <c r="D35" s="43" t="n">
+      <c r="D35" s="15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4167,9 +4899,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E4A63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4189,96 +4922,96 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="B3" s="44" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>Md Kamrul Hasan</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>https://github.com/Kamrul5242</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>entrepreneur-business-intelligence-cfo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>2.2.0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Signature ID</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>MKH-EBIC-2.2.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>MIT — attribution required</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Default currency</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>BDT (all 34 supported)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Notice</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>This workbook and its formula design are the work of Md Kamrul Hasan. The MIT License permits reuse and modification provided this attribution is retained in all copies and substantial portions.</t>
         </is>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.0</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.1</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.0</t>
+          <t>2.2.1</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.0</t>
+          <t>MKH-EBIC-2.2.1</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.0  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.1</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.2</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.2.2</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.1</t>
+          <t>MKH-EBIC-2.2.2</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.1  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.2</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.3</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.3</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.2</t>
+          <t>MKH-EBIC-2.2.3</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.2  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.3</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.4</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.4</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.3</t>
+          <t>MKH-EBIC-2.2.4</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.3  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.4</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.5</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.5</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.4</t>
+          <t>MKH-EBIC-2.2.5</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.4  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.5</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.6</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.6</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.5</t>
+          <t>MKH-EBIC-2.2.6</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.5  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -822,7 +822,7 @@
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Change this to switch every currency symbol in the workbook.
-Md Kamrul Hasan · MKH-EBIC-2.2.6</t>
+Md Kamrul Hasan · MKH-EBIC-2.2.7</t>
       </text>
     </comment>
   </commentList>
@@ -1682,7 +1682,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.7  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.7  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.7  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.7  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.7  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B6" s="58" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.7</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>MKH-EBIC-2.2.6</t>
+          <t>MKH-EBIC-2.2.7</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.6  ·  Attribution required under MIT License</t>
+          <t>◆ Md Kamrul Hasan  ·  https://github.com/Kamrul5242  ·  Digital Signature MKH-EBIC-2.2.7  ·  Attribution required under MIT License</t>
         </is>
       </c>
     </row>

--- a/assets/cfo-premium-dashboard.xlsx
+++ b/assets/cfo-premium-dashboard.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Setup" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Dashboard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Scenarios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Trend" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ref" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signature" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="0. Start Here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. Setup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. Scenarios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Trend" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ref" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Signature" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0. Start Here'!$A$1:$H$48</definedName>
@@ -588,14 +588,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -614,7 +614,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -654,8 +654,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -678,7 +678,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <plotArea>
@@ -693,14 +693,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -725,14 +725,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -760,8 +760,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -787,8 +787,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -830,7 +830,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -845,9 +845,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -857,7 +857,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -872,9 +872,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
